--- a/results/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -483,10 +483,10 @@
         <v>-0.019</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -510,10 +510,10 @@
         <v>-0.037</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.038</v>
+        <v>-0.037</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.001000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.045</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.029</v>
+        <v>-0.014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.016</v>
+        <v>-0.002</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.061</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.044</v>
+        <v>0.011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.017</v>
+        <v>0.035</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -591,10 +591,10 @@
         <v>0.097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -645,10 +645,10 @@
         <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -672,10 +672,10 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -699,10 +699,10 @@
         <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.041</v>
+        <v>-0.042</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03299999999999999</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -726,10 +726,10 @@
         <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.017</v>
+        <v>-0.018</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -807,10 +807,10 @@
         <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -834,10 +834,10 @@
         <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.012</v>
+        <v>-0.013</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -861,10 +861,10 @@
         <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.005999999999999998</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -888,10 +888,10 @@
         <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="E17" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -915,10 +915,10 @@
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -969,10 +969,10 @@
         <v>0.077</v>
       </c>
       <c r="D20" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="E20" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -996,10 +996,10 @@
         <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.022</v>
+        <v>-0.023</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.002999999999999999</v>
+        <v>-0.004</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1023,10 +1023,10 @@
         <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.055</v>
+        <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>0.058</v>
+        <v>0.063</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1050,10 +1050,10 @@
         <v>0.197</v>
       </c>
       <c r="D23" t="n">
-        <v>0.068</v>
+        <v>0.065</v>
       </c>
       <c r="E23" t="n">
-        <v>0.129</v>
+        <v>0.132</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1077,10 +1077,10 @@
         <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.043</v>
+        <v>-0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1104,10 +1104,10 @@
         <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.028</v>
+        <v>-0.027</v>
       </c>
       <c r="E25" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1131,10 +1131,10 @@
         <v>-0.128</v>
       </c>
       <c r="D26" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="E26" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1158,10 +1158,10 @@
         <v>0.227</v>
       </c>
       <c r="D27" t="n">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2</v>
+        <v>0.205</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1185,10 +1185,10 @@
         <v>0.392</v>
       </c>
       <c r="D28" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="E28" t="n">
-        <v>0.357</v>
+        <v>0.362</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1212,10 +1212,10 @@
         <v>-0.401</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.048</v>
+        <v>-0.038</v>
       </c>
       <c r="E29" t="n">
-        <v>0.353</v>
+        <v>0.363</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1239,10 +1239,10 @@
         <v>0.107</v>
       </c>
       <c r="D30" t="n">
-        <v>0.044</v>
+        <v>0.042</v>
       </c>
       <c r="E30" t="n">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01</v>
+        <v>-0.013</v>
       </c>
       <c r="E31" t="n">
-        <v>0.031</v>
+        <v>0.028</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1293,10 +1293,10 @@
         <v>-0.066</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.058</v>
+        <v>-0.057</v>
       </c>
       <c r="E32" t="n">
-        <v>0.008</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1388,22 +1388,22 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7100.892033747257</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="C2" t="n">
-        <v>0.994936431681357</v>
+        <v>0.9957648995493169</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1288663006716531</v>
+        <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.612879304103456</v>
+        <v>1.678870188120528</v>
       </c>
       <c r="F2" t="n">
-        <v>1.125850702242218</v>
+        <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.612462982328197</v>
+        <v>1.678043421071839</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.461956362663354</v>
+        <v>1.588437647332135</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1010045641510126</v>
+        <v>0.09951383604476764</v>
       </c>
       <c r="D2" t="n">
-        <v>1.263991054653204</v>
+        <v>1.393394112720966</v>
       </c>
       <c r="E2" t="n">
-        <v>1.659921670673504</v>
+        <v>1.783481181943303</v>
       </c>
       <c r="F2" t="n">
-        <v>1.764648253054441e-47</v>
+        <v>2.351594952909258e-57</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002072161518831284</v>
+        <v>0.002289543090502433</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01995924153242864</v>
+        <v>0.0200435016019184</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03704723304346489</v>
+        <v>-0.03699499817332852</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04119155608112746</v>
+        <v>0.04157408435433338</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9173124703556581</v>
+        <v>0.9090565031154842</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.02825711224060222</v>
+        <v>-0.02760529193760392</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05344011381589339</v>
+        <v>0.0518165195556562</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1329978106494746</v>
+        <v>-0.1291638040709055</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07648358616827018</v>
+        <v>0.07395322019569764</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5969704215684793</v>
+        <v>0.5942060998044849</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003462466765246554</v>
+        <v>0.001979053634585247</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03486573768540872</v>
+        <v>0.03523203519821218</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06798934348129736</v>
+        <v>-0.06707446645595813</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06868183683434666</v>
+        <v>0.07103257372512864</v>
       </c>
       <c r="F5" t="n">
-        <v>0.992076452274566</v>
+        <v>0.9552047922716995</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03376606220306323</v>
+        <v>0.03340001985125012</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03402217029001788</v>
+        <v>0.03286258508177218</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03291616624126045</v>
+        <v>-0.03100946334790662</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1004482906473869</v>
+        <v>0.09780950305040685</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3209671766959148</v>
+        <v>0.3094608416342961</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01603380109372001</v>
+        <v>-0.01514663535578088</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03450476783125448</v>
+        <v>0.03537760492293865</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08366190333789503</v>
+        <v>-0.08448546686402755</v>
       </c>
       <c r="E7" t="n">
-        <v>0.051594301150455</v>
+        <v>0.05419219615246579</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6421580262149722</v>
+        <v>0.6685478054594494</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01587882978040083</v>
+        <v>-0.0139145210057712</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03492384799078779</v>
+        <v>0.03582624135777854</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08432831404389643</v>
+        <v>-0.0841326637684565</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05257065448309478</v>
+        <v>0.0563036217569141</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6493465881146407</v>
+        <v>0.6977281223699652</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02764182645717018</v>
+        <v>-0.02606854715545236</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03436581468053673</v>
+        <v>0.03445174256130681</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09499758553040002</v>
+        <v>-0.09359272178025943</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03971393261605968</v>
+        <v>0.0414556274693547</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4212001876130719</v>
+        <v>0.4492485122499704</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1238393219826676</v>
+        <v>-0.1243555105431013</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0537381828247083</v>
+        <v>0.05548145045815721</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2291642249137248</v>
+        <v>-0.2330971552511327</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01851441905161043</v>
+        <v>-0.01561386583506992</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02119492658954981</v>
+        <v>0.02500089100745368</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07401589961265695</v>
+        <v>0.07368505338474862</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05389906152024387</v>
+        <v>0.05628990533964608</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03162431976752972</v>
+        <v>-0.03664113377412656</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1796561189928436</v>
+        <v>0.1840112405436238</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1696803293456421</v>
+        <v>0.1905249193656604</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.05861996856433684</v>
+        <v>-0.0603922635557705</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05629973303962031</v>
+        <v>0.06009378790448144</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1689654176612124</v>
+        <v>-0.1781739235431429</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05172548053253872</v>
+        <v>0.05738939643160186</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2977770775366366</v>
+        <v>0.3149128220217311</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.03962160606828451</v>
+        <v>-0.03918292931079827</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0531645603746102</v>
+        <v>0.05709010836228825</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1438222296564258</v>
+        <v>-0.1510774855743722</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06457901751985676</v>
+        <v>0.07271162695277567</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4561124449419066</v>
+        <v>0.4925019956822226</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.086625174524172</v>
+        <v>-0.08961924675638726</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05417245208231985</v>
+        <v>0.05597301997478082</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1928012295597408</v>
+        <v>-0.1993243500128987</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01955088051139676</v>
+        <v>0.02008585650012421</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1098065606951895</v>
+        <v>0.1093514311924686</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.07918918637214029</v>
+        <v>-0.07971063832368433</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05288088314170214</v>
+        <v>0.0548670256323885</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1828338128005478</v>
+        <v>-0.1872480325020018</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02445544005626721</v>
+        <v>0.02782675585463312</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1342628915596395</v>
+        <v>0.1462801854677666</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07384401163525674</v>
+        <v>-0.07536173463392269</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05322263289394042</v>
+        <v>0.05394309282729033</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1781584552697767</v>
+        <v>-0.1810882537901127</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03047043199926328</v>
+        <v>0.03036478452226728</v>
       </c>
       <c r="F16" t="n">
-        <v>0.165303043732254</v>
+        <v>0.1623955437074894</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.007274360321028624</v>
+        <v>-0.007508945504431109</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0544422749919164</v>
+        <v>0.0568972604168901</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1139792585416104</v>
+        <v>-0.1190255267405321</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09943053789955317</v>
+        <v>0.1040076357316699</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8937062125082319</v>
+        <v>0.8950050450910965</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0255345189896411</v>
+        <v>-0.02702123264755607</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05164284206387138</v>
+        <v>0.05498884081168753</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1267526294941192</v>
+        <v>-0.1347973801900699</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07568359151483696</v>
+        <v>0.08075491489495776</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6209922963545045</v>
+        <v>0.6231472128909764</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0807386911463899</v>
+        <v>-0.08375751060329234</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05287926008009732</v>
+        <v>0.05360990234935117</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1843801364325073</v>
+        <v>-0.1888309884227299</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02290275413972745</v>
+        <v>0.02131596721614518</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1267983485531143</v>
+        <v>0.1182052092143447</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1286052800279295</v>
+        <v>-0.1311358803541576</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05218726582743615</v>
+        <v>0.05406282801340151</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2308904415013223</v>
+        <v>-0.2370970761628076</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02632011855453675</v>
+        <v>-0.0251746845455075</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01372796801763353</v>
+        <v>0.01528225980615014</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1236060059552661</v>
+        <v>-0.1241875106822867</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05332022144783298</v>
+        <v>0.05616362862747454</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2281117196407189</v>
+        <v>-0.2342662000332196</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01910029226981332</v>
+        <v>-0.01410882133135385</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02043940297359321</v>
+        <v>0.02702384518809445</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.07179494999624639</v>
+        <v>-0.07269691488818508</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05565445388509206</v>
+        <v>0.05654139166683251</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1808756751902721</v>
+        <v>-0.1835160061909499</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03728577519777934</v>
+        <v>0.03812217641457977</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1970462631560097</v>
+        <v>0.1985376076796661</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01576099827420017</v>
+        <v>-0.01550704881921876</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05096674476645334</v>
+        <v>0.05396301665233488</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.115653982425694</v>
+        <v>-0.1212726179549303</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08413198587729367</v>
+        <v>0.09025852031649281</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7571383398054766</v>
+        <v>0.7738333321942765</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.01631769804138278</v>
+        <v>-0.01712641609733917</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04760221883346801</v>
+        <v>0.04898189205297217</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1096163325391743</v>
+        <v>-0.1131291604157933</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07698093645640879</v>
+        <v>0.07887632822111498</v>
       </c>
       <c r="F24" t="n">
-        <v>0.73175434036665</v>
+        <v>0.7266029520031178</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.019177792552909</v>
+        <v>0.01900783443856898</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0247357542307138</v>
+        <v>0.02561343601916734</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02930339486972431</v>
+        <v>-0.03119357767931998</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06765897997554232</v>
+        <v>0.06920924655645795</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4381585332171052</v>
+        <v>0.4580243001316242</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.01032648080273423</v>
+        <v>-0.01141783923973179</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03148296604976158</v>
+        <v>0.03075125430929364</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0720319603867642</v>
+        <v>-0.07168919016537946</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05137899878129573</v>
+        <v>0.04885351168591589</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7429100310069607</v>
+        <v>0.7104165557437996</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.008158708750964659</v>
+        <v>0.008263771382752945</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0315012687220047</v>
+        <v>0.03117627639559384</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.05358264341148266</v>
+        <v>-0.0528406075246772</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06990006091341197</v>
+        <v>0.06936815029018309</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7956381759561943</v>
+        <v>0.7909586063851286</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.04444698902099124</v>
+        <v>0.04411323392421416</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03183562453496349</v>
+        <v>0.03148338007871244</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.01794968849287691</v>
+        <v>-0.01759305714164803</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1068436665348594</v>
+        <v>0.1058195249900764</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1626723387565998</v>
+        <v>0.1611664122763737</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.009696012066446276</v>
+        <v>-0.01093490893956167</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03241355659155709</v>
+        <v>0.03231638714325723</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07322541559674905</v>
+        <v>-0.07427386385079909</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0538333914638565</v>
+        <v>0.05240404597167575</v>
       </c>
       <c r="F29" t="n">
-        <v>0.764837446579744</v>
+        <v>0.7350840751185997</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2292296347053535</v>
+        <v>0.230026785190034</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04162304148607206</v>
+        <v>0.04275687264023308</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1476499724656357</v>
+        <v>0.1462248547236111</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3108092969450713</v>
+        <v>0.3138287156564569</v>
       </c>
       <c r="F30" t="n">
-        <v>3.644258234333755e-08</v>
+        <v>7.453607464503637e-08</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4914012775125147</v>
+        <v>-0.007701111887135847</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01013311587660631</v>
+        <v>0.004563797415138304</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4715407353431953</v>
+        <v>-0.01664599045354392</v>
       </c>
       <c r="E31" t="n">
-        <v>0.511261819681834</v>
+        <v>0.001243766679272222</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.09151972193448024</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0005329433211200373</v>
+        <v>0.001336822150411828</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001499921564706946</v>
+        <v>0.001449434599930931</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.00240684892534054</v>
+        <v>-0.001504017463399018</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003472735567580615</v>
+        <v>0.004177661764222674</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7223542733514146</v>
+        <v>0.35636901320012</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.001085178604865215</v>
+        <v>0.4906715993267194</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001466634309828704</v>
+        <v>0.01020038761332357</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003959729030620233</v>
+        <v>0.4706792069762567</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001789371820889804</v>
+        <v>0.510663991677182</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4593541044738016</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.0008117248737531974</v>
+        <v>-0.0008959807646594218</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001797786399366401</v>
+        <v>0.001756049857289176</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004335321468407286</v>
+        <v>-0.004337775240002908</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00271187172090089</v>
+        <v>0.002545813710684064</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6516194796614238</v>
+        <v>0.6098937492520438</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.008500139985020335</v>
+        <v>-0.001002562195601323</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0234333386491854</v>
+        <v>0.001411716497337636</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.03742835980491353</v>
+        <v>-0.003769475686764125</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05442863977495419</v>
+        <v>0.001764351295561479</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7168013248744345</v>
+        <v>0.4775971888880657</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2310,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.008329716011993627</v>
+        <v>0.009570099507611826</v>
       </c>
       <c r="C36" t="n">
-        <v>0.004457809928374381</v>
+        <v>0.02352815839717277</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0004074308975452363</v>
+        <v>-0.03654424357340044</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01706686292153249</v>
+        <v>0.05568444258862409</v>
       </c>
       <c r="F36" t="n">
-        <v>0.06168309653147422</v>
+        <v>0.6841909551554408</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.350970771285248</v>
+        <v>-2.68060017980294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4605522587714034</v>
+        <v>0.4771933030981267</v>
       </c>
       <c r="D2" t="n">
-        <v>3.313590542287848e-07</v>
+        <v>1.93818176827037e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02128055977478192</v>
+        <v>-0.02542074333516159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09751395156308111</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.827249191641336</v>
+        <v>0.7997554080121703</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2245966634275915</v>
+        <v>0.2244463748843408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2329354389845562</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3349449904957182</v>
+        <v>0.3364439424069164</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8167052829997485</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1617156577703267</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>4.412210487480358e-07</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03599538577094948</v>
+        <v>0.03527526670387294</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1898688322218615</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8496380437366924</v>
+        <v>0.8539945454713553</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2765708211818085</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1824472225347018</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.129545920374235</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1102648615599912</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1853641405651108</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5519401263365121</v>
+        <v>0.5954095400432468</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8745743640527194</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1615402513662274</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>6.164188141358052e-08</v>
+        <v>2.539495077342719e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04349724922704642</v>
+        <v>-0.04456520772617057</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2655215602978132</v>
+        <v>0.2604021031716314</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8698743077153893</v>
+        <v>0.8641137091517844</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2685655156863916</v>
+        <v>-0.2737623724798145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2761865361461748</v>
+        <v>0.2787881385465063</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3308484806726052</v>
+        <v>0.3261132423877634</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08406558527820192</v>
+        <v>0.08100487957118158</v>
       </c>
       <c r="C12" t="n">
-        <v>0.251020166800007</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7377037334343584</v>
+        <v>0.7550514391424689</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04159103469582721</v>
+        <v>0.03917827337461771</v>
       </c>
       <c r="C13" t="n">
-        <v>0.255561465250315</v>
+        <v>0.2572958805743772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8707201879025983</v>
+        <v>0.8789745077123736</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05097157642059893</v>
+        <v>-0.05296103812307912</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2615504699624188</v>
+        <v>0.2610089865588722</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8454850334004391</v>
+        <v>0.8392062624375538</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1235593461635321</v>
+        <v>0.1181322726534163</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2569613848518211</v>
+        <v>0.2572294350577189</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6306245929938302</v>
+        <v>0.6460556128984085</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.002490750131026257</v>
+        <v>-0.00400098624037939</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2457746491930773</v>
+        <v>0.2383903410311194</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9919141495524532</v>
+        <v>0.9866094604655136</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1110262478895003</v>
+        <v>0.1057185310395308</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2594324060220158</v>
+        <v>0.2543340222421757</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6686814903924607</v>
+        <v>0.6776529122567302</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1338440250599403</v>
+        <v>-0.1377694895733253</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2694490717592011</v>
+        <v>0.2636874203313639</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6193779257550096</v>
+        <v>0.6013412201546287</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02068301206114321</v>
+        <v>-0.0255715409422322</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2629683391871477</v>
+        <v>0.2527597901538112</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9373093461992266</v>
+        <v>0.9194160355966682</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0686991433762508</v>
+        <v>-0.07344622569376394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2617458461247386</v>
+        <v>0.2674578609541013</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7929629071620667</v>
+        <v>0.7836169672222786</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2112158738988716</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2400889859196068</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3790001987958982</v>
+        <v>0.3983578134719856</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.159933319308369</v>
+        <v>-0.1704634573362025</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2649283257747139</v>
+        <v>0.2696748454965907</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5460529306471213</v>
+        <v>0.5273167196806369</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4920005620651325</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2884409459397611</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08805953197431808</v>
+        <v>0.08105838975171867</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9425285809878476</v>
+        <v>0.9366864721074269</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1559773650465781</v>
+        <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>1.515312581506736e-09</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5768512495314141</v>
+        <v>-0.5776106069409676</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1130405709043027</v>
+        <v>0.1143619392421805</v>
       </c>
       <c r="D25" t="n">
-        <v>3.342294640071132e-07</v>
+        <v>4.401383208103756e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2384858887162336</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1457315480836286</v>
+        <v>0.1503781926377478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1017404238903948</v>
+        <v>0.1145360411757809</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04585234373593617</v>
+        <v>-0.04350476117998649</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1593109532353293</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7734870970055308</v>
+        <v>0.7872365295400219</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07857740431296747</v>
+        <v>-0.07514354096975731</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1565335672967476</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6156785148897228</v>
+        <v>0.6414556246120153</v>
       </c>
     </row>
     <row r="29">
@@ -2807,45 +2807,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09755305493394664</v>
+        <v>0.09749293462742098</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1499487653516257</v>
+        <v>0.1543265796290168</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5153202832397639</v>
+        <v>0.5275624553510017</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.006860378637723895</v>
+        <v>-0.004129656026475424</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006945236405256705</v>
+        <v>0.02222260881033181</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3232594861617505</v>
+        <v>0.8525770672961283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002646425713821547</v>
+        <v>0.006335499136474501</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007095424075339026</v>
+        <v>0.006871422968197188</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7091660102282209</v>
+        <v>0.3565249957666434</v>
       </c>
     </row>
     <row r="32">
@@ -2855,45 +2855,45 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004895000819746557</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008684655396149939</v>
+        <v>0.008304876992454852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5730005966817302</v>
+        <v>0.5461741835341496</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2261835420647834</v>
+        <v>-0.00241813341219285</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1139281184793711</v>
+        <v>0.007135781003458538</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04710910483736543</v>
+        <v>0.7347043603418298</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01540023496026497</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0213723694247541</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D34" t="n">
-        <v>0.47117565131408</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.227</v>
+        <v>-0.008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.022</v>
+        <v>-0.001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.205</v>
+        <v>0.007</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.143</v>
+        <v>-0.066</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.044</v>
+        <v>-0.058</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09899999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.054</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>-0.027</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.024</v>
+        <v>0.041</v>
       </c>
       <c r="D10" t="n">
-        <v>0.026</v>
+        <v>0.037</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.001999999999999998</v>
+        <v>0.004000000000000004</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>0.007</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.008</v>
+        <v>0.024</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>-0.017</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.107</v>
+        <v>-0.074</v>
       </c>
       <c r="D12" t="n">
-        <v>0.043</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>0.064</v>
+        <v>0.034</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007</v>
+        <v>0.034</v>
       </c>
       <c r="D13" t="n">
-        <v>0.024</v>
+        <v>-0.008</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.017</v>
+        <v>0.026</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.128</v>
+        <v>-0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.021</v>
+        <v>-0.013</v>
       </c>
       <c r="E14" t="n">
-        <v>0.107</v>
+        <v>0.028</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>0.032</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.013</v>
+        <v>0.033</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.008</v>
+        <v>-0.001000000000000001</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
       <c r="D16" t="n">
-        <v>0.033</v>
+        <v>0.006</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.001000000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.046</v>
+        <v>-0.401</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.002</v>
+        <v>-0.039</v>
       </c>
       <c r="E17" t="n">
-        <v>0.044</v>
+        <v>0.362</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.392</v>
+        <v>-0.014</v>
       </c>
       <c r="D18" t="n">
-        <v>0.029</v>
+        <v>-0.002</v>
       </c>
       <c r="E18" t="n">
-        <v>0.363</v>
+        <v>0.012</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>-0.143</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001</v>
+        <v>-0.044</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007</v>
+        <v>0.09899999999999999</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.197</v>
+        <v>-0.019</v>
       </c>
       <c r="D20" t="n">
-        <v>0.064</v>
+        <v>-0.022</v>
       </c>
       <c r="E20" t="n">
-        <v>0.133</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.074</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.04</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.034</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.023</v>
+        <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="E23" t="n">
-        <v>0.017</v>
+        <v>-0.003</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.401</v>
+        <v>0.022</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.039</v>
+        <v>0.015</v>
       </c>
       <c r="E24" t="n">
-        <v>0.362</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.041</v>
+        <v>-0.024</v>
       </c>
       <c r="D25" t="n">
-        <v>0.037</v>
+        <v>0.026</v>
       </c>
       <c r="E25" t="n">
-        <v>0.004000000000000004</v>
+        <v>-0.001999999999999998</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.066</v>
+        <v>0.197</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.058</v>
+        <v>0.064</v>
       </c>
       <c r="E27" t="n">
-        <v>0.008</v>
+        <v>0.133</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.041</v>
+        <v>0.046</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.013</v>
+        <v>-0.002</v>
       </c>
       <c r="E28" t="n">
-        <v>0.028</v>
+        <v>0.044</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="D29" t="n">
         <v>0.022</v>
       </c>
-      <c r="D29" t="n">
-        <v>0.015</v>
-      </c>
       <c r="E29" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.054</v>
+        <v>0.005</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.027</v>
+        <v>-0.013</v>
       </c>
       <c r="E30" t="n">
-        <v>0.027</v>
+        <v>-0.008</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.019</v>
+        <v>0.107</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.022</v>
+        <v>0.043</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.014</v>
+        <v>-0.128</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.002</v>
+        <v>0.021</v>
       </c>
       <c r="E32" t="n">
-        <v>0.012</v>
+        <v>0.107</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>0.392</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003</v>
+        <v>0.029</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.003</v>
+        <v>0.363</v>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -1424,7 +1424,7 @@
         <v>0.13297606180212</v>
       </c>
       <c r="E2" t="n">
-        <v>1.682349091155619</v>
+        <v>1.68234909115562</v>
       </c>
       <c r="F2" t="n">
         <v>1.126973544354103</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.588422507365227</v>
+        <v>1.588422507365228</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09950879751532972</v>
+        <v>0.09950879751533108</v>
       </c>
       <c r="D2" t="n">
-        <v>1.393388848090292</v>
+        <v>1.39338884809029</v>
       </c>
       <c r="E2" t="n">
-        <v>1.783456166640162</v>
+        <v>1.783456166640165</v>
       </c>
       <c r="F2" t="n">
-        <v>2.327001655347131e-57</v>
+        <v>2.327001655354998e-57</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002157202703634708</v>
+        <v>0.002157202703634746</v>
       </c>
       <c r="C3" t="n">
         <v>0.02004412832739044</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03712856691954963</v>
+        <v>-0.03712856691954959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04144297232681905</v>
+        <v>0.04144297232681908</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9142950096096367</v>
+        <v>0.9142950096096353</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1541,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.02806347567340359</v>
+        <v>-0.02806347567340356</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05180741466195353</v>
+        <v>0.05180741466195352</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1296041425429648</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07347719119615767</v>
+        <v>0.07347719119615768</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5880331806434524</v>
+        <v>0.5880331806434529</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1566,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002136000897429323</v>
+        <v>0.002136000897429317</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03521890701594482</v>
+        <v>0.0352189070159448</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06689178842868755</v>
+        <v>-0.06689178842868751</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0711637902235462</v>
+        <v>0.07116379022354616</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9516385362649575</v>
+        <v>0.9516385362649576</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03303202308651729</v>
+        <v>0.03303202308651724</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03286800426819425</v>
+        <v>0.03286800426819424</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03138808152285221</v>
+        <v>-0.03138808152285224</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09745212769588679</v>
+        <v>0.09745212769588671</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3149015555617194</v>
+        <v>0.3149015555617202</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1619,16 +1619,16 @@
         <v>-0.0152122870861078</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03536389523671278</v>
+        <v>0.03536389523671277</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08452424810311243</v>
+        <v>-0.0845242481031124</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05409967393089683</v>
+        <v>0.05409967393089682</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6670760911481435</v>
+        <v>0.6670760911481436</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1641,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01369113270818714</v>
+        <v>-0.01369113270818715</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0358374956507626</v>
+        <v>0.03583749565076259</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08393133347979266</v>
+        <v>-0.08393133347979263</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05654906806341838</v>
+        <v>0.05654906806341834</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7024363340113147</v>
+        <v>0.7024363340113144</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1666,16 +1666,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02619917626172892</v>
+        <v>-0.02619917626172891</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03445373577537433</v>
+        <v>0.03445373577537431</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0937272575143218</v>
+        <v>-0.09372725751432176</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04132890499086396</v>
+        <v>0.04132890499086394</v>
       </c>
       <c r="F9" t="n">
         <v>0.4470058874486471</v>
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1242064437800989</v>
+        <v>-0.124206443780099</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05548417525012689</v>
+        <v>0.05548417525012692</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2329534289822562</v>
+        <v>-0.2329534289822563</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01545945857794154</v>
+        <v>-0.01545945857794155</v>
       </c>
       <c r="F10" t="n">
         <v>0.02518246006139378</v>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07320420542333134</v>
+        <v>0.07320420542333132</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05628688228526357</v>
+        <v>0.05628688228526354</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03711605665783083</v>
+        <v>-0.03711605665783078</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1835244675044935</v>
+        <v>0.1835244675044934</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1934107016225541</v>
+        <v>0.193410701622554</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.06076403853532333</v>
+        <v>-0.06076403853532326</v>
       </c>
       <c r="C12" t="n">
         <v>0.06002138315034827</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1784037878122852</v>
+        <v>-0.1784037878122851</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05687571074163852</v>
+        <v>0.05687571074163859</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3113596568518611</v>
+        <v>0.3113596568518616</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.03935267962244717</v>
+        <v>-0.03935267962244716</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05702989918185173</v>
+        <v>0.05702989918185167</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1511292280608268</v>
+        <v>-0.1511292280608267</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07242386881593252</v>
+        <v>0.07242386881593241</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4901715914374869</v>
+        <v>0.4901715914374866</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.08994407386175085</v>
+        <v>-0.08994407386175092</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05595151464980278</v>
+        <v>0.05595151464980275</v>
       </c>
       <c r="D14" t="n">
         <v>-0.1996070274558295</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01971887973232782</v>
+        <v>0.01971887973232768</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1079368395669103</v>
+        <v>0.1079368395669098</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.07972002010245764</v>
+        <v>-0.07972002010245767</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05482862722193883</v>
+        <v>0.05482862722193887</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1871821547792302</v>
+        <v>-0.1871821547792303</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02774211457431487</v>
+        <v>0.02774211457431491</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1459503711242125</v>
+        <v>0.1459503711242126</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07580821482423755</v>
+        <v>-0.07580821482423769</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05391836373954744</v>
+        <v>0.05391836373954741</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1814862658590809</v>
+        <v>-0.181486265859081</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02986983621060582</v>
+        <v>0.02986983621060563</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1597296574439616</v>
+        <v>0.1597296574439606</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.007958708481944608</v>
+        <v>-0.007958708481944632</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0568658590176258</v>
+        <v>0.05686585901762571</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1194137441064234</v>
+        <v>-0.1194137441064233</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1034963271425342</v>
+        <v>0.103496327142534</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8886948895826455</v>
+        <v>0.8886948895826451</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02674600637292568</v>
+        <v>-0.02674600637292563</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05495082849883504</v>
+        <v>0.05495082849883502</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1344476511512796</v>
+        <v>-0.1344476511512795</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08095563840542822</v>
+        <v>0.0809556384054282</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6264523959201853</v>
+        <v>0.6264523959201856</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.08417048724369865</v>
+        <v>-0.08417048724369866</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05356575306273122</v>
+        <v>0.05356575306273117</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1891574340514179</v>
+        <v>-0.1891574340514178</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02081645956402065</v>
+        <v>0.02081645956402052</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1161016281223219</v>
+        <v>0.1161016281223215</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1944,16 +1944,16 @@
         <v>-0.1315545875635716</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05402663862558477</v>
+        <v>0.05402663862558474</v>
       </c>
       <c r="D20" t="n">
         <v>-0.2374448534754783</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02566432165166485</v>
+        <v>-0.02566432165166498</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01489200108264313</v>
+        <v>0.01489200108264303</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.07290986245855967</v>
+        <v>-0.07290986245855982</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05651076265826972</v>
+        <v>0.05651076265826976</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1836689220076593</v>
+        <v>-0.1836689220076595</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03784919709053994</v>
+        <v>0.03784919709053987</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1969832133925169</v>
+        <v>0.1969832133925162</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01550122276689234</v>
+        <v>-0.01550122276689241</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05392880208198836</v>
+        <v>0.05392880208198828</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1211997325769782</v>
+        <v>-0.1211997325769781</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09019728704319353</v>
+        <v>0.0901972870431933</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7737764608404205</v>
+        <v>0.7737764608404192</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.01736702286559949</v>
+        <v>-0.01736702286559948</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04895754327588753</v>
+        <v>0.04895754327588756</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1133220444579001</v>
+        <v>-0.1133220444579002</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07858799872670116</v>
+        <v>0.07858799872670123</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7227870755887473</v>
+        <v>0.7227870755887478</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01900414985650927</v>
+        <v>0.01900414985650926</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02562283647390875</v>
+        <v>0.0256228364739088</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03121568681411115</v>
+        <v>-0.03121568681411126</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06922398652712969</v>
+        <v>0.06922398652712977</v>
       </c>
       <c r="F25" t="n">
-        <v>0.458276403431649</v>
+        <v>0.4582764034316501</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.01136511239972217</v>
+        <v>-0.01136511239972224</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03076545132329943</v>
+        <v>0.03076545132329945</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.07166428896150918</v>
+        <v>-0.07166428896150931</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04893406416206485</v>
+        <v>0.04893406416206483</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7118210062148231</v>
+        <v>0.7118210062148216</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.008288872114818061</v>
+        <v>0.008288872114817944</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03118021288371117</v>
+        <v>0.03118021288371118</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0528232221675476</v>
+        <v>-0.05282322216754776</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06940096639718372</v>
+        <v>0.06940096639718364</v>
       </c>
       <c r="F27" t="n">
-        <v>0.790364305050885</v>
+        <v>0.7903643050508879</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.04441792109265486</v>
+        <v>0.04441792109265476</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03147225308209888</v>
+        <v>0.0314722530820989</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.01726656146058866</v>
+        <v>-0.0172665614605888</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1061024036458984</v>
+        <v>0.1061024036458983</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1581455893971977</v>
+        <v>0.1581455893971989</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01111026890206905</v>
+        <v>-0.01111026890206916</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03230457849540542</v>
+        <v>0.03230457849540543</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0744260792888108</v>
+        <v>-0.07442607928881094</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0522055414846727</v>
+        <v>0.05220554148467262</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7309046284390859</v>
+        <v>0.7309046284390834</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2303472064753823</v>
+        <v>0.2303472064753822</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04274619914367981</v>
+        <v>0.04274619914367982</v>
       </c>
       <c r="D30" t="n">
         <v>0.1465661956777929</v>
@@ -2203,7 +2203,7 @@
         <v>0.3141282172729716</v>
       </c>
       <c r="F30" t="n">
-        <v>7.096210791271779e-08</v>
+        <v>7.096210791271882e-08</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2212,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.001023762880892497</v>
+        <v>0.001323773742398878</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001412550988754019</v>
+        <v>0.001449666664927174</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.003792311945176817</v>
+        <v>-0.001517520710446678</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001744786183391824</v>
+        <v>0.004165068195244434</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4685982250511583</v>
+        <v>0.3611598015227342</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2237,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0008847896531368739</v>
+        <v>0.4907763416057432</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001755881165775725</v>
+        <v>0.01020349621388542</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004326253499189499</v>
+        <v>0.4707778565101369</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002556674192915751</v>
+        <v>0.5107748267013494</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6143311968318106</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2262,23 +2262,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.007684909964816858</v>
+        <v>-0.001023762880892497</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004562970024586866</v>
+        <v>0.001412550988754018</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.01662816687554296</v>
+        <v>-0.003792311945176817</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001258346945909245</v>
+        <v>0.001744786183391822</v>
       </c>
       <c r="F33" t="n">
-        <v>0.09214489260396649</v>
+        <v>0.4685982250511579</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.009295972736054448</v>
+        <v>0.009295972736054522</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02351946149446093</v>
+        <v>0.02351946149446091</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.03680132472886557</v>
+        <v>-0.03680132472886545</v>
       </c>
       <c r="E34" t="n">
-        <v>0.05539327020097446</v>
+        <v>0.0553932702009745</v>
       </c>
       <c r="F34" t="n">
-        <v>0.692661358138289</v>
+        <v>0.6926613581382863</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4907763416057432</v>
+        <v>-0.0008847896531368874</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01020349621388547</v>
+        <v>0.001755881165775706</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4707778565101369</v>
+        <v>-0.004326253499189475</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5107748267013495</v>
+        <v>0.0025566741929157</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.6143311968318013</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2337,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001323773742398876</v>
+        <v>-0.007684909964816873</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001449666664927172</v>
+        <v>0.004562970024586844</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.001517520710446677</v>
+        <v>-0.01662816687554293</v>
       </c>
       <c r="E36" t="n">
-        <v>0.004165068195244427</v>
+        <v>0.001258346945909186</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3611598015227346</v>
+        <v>0.09214489260396432</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.820303044554361</v>
+        <v>-2.820303044554362</v>
       </c>
       <c r="C2" t="n">
-        <v>0.509923439509295</v>
+        <v>0.5099234395092913</v>
       </c>
       <c r="D2" t="n">
-        <v>3.187077352409087e-08</v>
+        <v>3.18707735240834e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02464939576457213</v>
+        <v>-0.02464939576457235</v>
       </c>
       <c r="C3" t="n">
         <v>0.1003099681595394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8058894933269598</v>
+        <v>0.8058894933269581</v>
       </c>
     </row>
     <row r="4">
@@ -2434,13 +2434,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2249663577428586</v>
+        <v>0.2249663577428585</v>
       </c>
       <c r="C4" t="n">
         <v>0.2337176582603367</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3357703370011802</v>
+        <v>0.3357703370011803</v>
       </c>
     </row>
     <row r="5">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8191373674885462</v>
+        <v>0.8191373674885463</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734167828528217</v>
+        <v>0.1734167828528219</v>
       </c>
       <c r="D5" t="n">
-        <v>2.317989576597488e-06</v>
+        <v>2.317989576597531e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0365212576599634</v>
+        <v>0.03652125765996336</v>
       </c>
       <c r="C6" t="n">
         <v>0.1917132959179624</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8489178549322635</v>
+        <v>0.8489178549322636</v>
       </c>
     </row>
     <row r="7">
@@ -2485,10 +2485,10 @@
         <v>0.2789564326928405</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901139906226967</v>
+        <v>0.1901139906226968</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1422913540098489</v>
+        <v>0.1422913540098492</v>
       </c>
     </row>
     <row r="8">
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1068531552827688</v>
+        <v>0.1068531552827689</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1953287956048305</v>
+        <v>0.1953287956048307</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5843495250374457</v>
+        <v>0.5843495250374455</v>
       </c>
     </row>
     <row r="9">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8765772051307454</v>
+        <v>0.8765772051307453</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1697332036095896</v>
+        <v>0.1697332036095897</v>
       </c>
       <c r="D9" t="n">
-        <v>2.411578475116398e-07</v>
+        <v>2.411578475116438e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04447986866030648</v>
+        <v>-0.04447986866030693</v>
       </c>
       <c r="C10" t="n">
-        <v>0.260451332255926</v>
+        <v>0.2604513322559264</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8643967854929914</v>
+        <v>0.8643967854929903</v>
       </c>
     </row>
     <row r="11">
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2727472209256582</v>
+        <v>-0.2727472209256581</v>
       </c>
       <c r="C11" t="n">
         <v>0.2791278961561445</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3284995130487426</v>
+        <v>0.3284995130487427</v>
       </c>
     </row>
     <row r="12">
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07889678868393121</v>
+        <v>0.07889678868393106</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596148796948629</v>
+        <v>0.2596148796948633</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7612045862333771</v>
+        <v>0.7612045862333778</v>
       </c>
     </row>
     <row r="13">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0401939304148166</v>
+        <v>0.04019393041481645</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2574204041328301</v>
+        <v>0.2574204041328311</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8759217249006983</v>
+        <v>0.8759217249006992</v>
       </c>
     </row>
     <row r="14">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04910228165084263</v>
+        <v>-0.04910228165084252</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2612561015991028</v>
+        <v>0.2612561015991035</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8509182551619321</v>
+        <v>0.8509182551619328</v>
       </c>
     </row>
     <row r="15">
@@ -2613,10 +2613,10 @@
         <v>0.1160743543422993</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2571236264961845</v>
+        <v>0.2571236264961856</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6516767631412977</v>
+        <v>0.6516767631412993</v>
       </c>
     </row>
     <row r="16">
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.002512421030225608</v>
+        <v>-0.002512421030225878</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2386078717504875</v>
+        <v>0.238607871750488</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9915988316144669</v>
+        <v>0.991598831614466</v>
       </c>
     </row>
     <row r="17">
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1088094847883379</v>
+        <v>0.1088094847883377</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2546184298925979</v>
+        <v>0.2546184298925984</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6691292855457309</v>
+        <v>0.6691292855457321</v>
       </c>
     </row>
     <row r="18">
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1371054629493655</v>
+        <v>-0.137105462949366</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2637238215346593</v>
+        <v>0.2637238215346601</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6031453060320012</v>
+        <v>0.603145306032001</v>
       </c>
     </row>
     <row r="19">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02469784288290731</v>
+        <v>-0.02469784288290738</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2529058254775156</v>
+        <v>0.2529058254775164</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9222052306173943</v>
+        <v>0.9222052306173945</v>
       </c>
     </row>
     <row r="20">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06845683158478705</v>
+        <v>-0.06845683158478712</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2673011584514005</v>
+        <v>0.2673011584514008</v>
       </c>
       <c r="D20" t="n">
         <v>0.7978707191500406</v>
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2086621675742927</v>
+        <v>0.2086621675742925</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442815662419177</v>
+        <v>0.2442815662419186</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3930013184626154</v>
+        <v>0.3930013184626175</v>
       </c>
     </row>
     <row r="22">
@@ -2725,10 +2725,10 @@
         <v>-0.1754067081881009</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2700541998112387</v>
+        <v>0.2700541998112392</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5159996811704795</v>
+        <v>0.5159996811704801</v>
       </c>
     </row>
     <row r="23">
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5004384224930729</v>
+        <v>-0.500438422493073</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870894861894648</v>
+        <v>0.2870894861894652</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08130839926920327</v>
+        <v>0.08130839926920354</v>
       </c>
     </row>
     <row r="24">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9379041483579631</v>
+        <v>0.9379041483579632</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1484949273354127</v>
+        <v>0.1484949273354128</v>
       </c>
       <c r="D24" t="n">
-        <v>2.683009814405772e-10</v>
+        <v>2.683009814405793e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2773,10 +2773,10 @@
         <v>-0.5776000776467408</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143336799033597</v>
+        <v>0.1143336799033598</v>
       </c>
       <c r="D25" t="n">
-        <v>4.37481595543926e-07</v>
+        <v>4.374815955439373e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2357452695510329</v>
+        <v>0.2357452695510327</v>
       </c>
       <c r="C26" t="n">
         <v>0.1505208025229895</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1173024423291908</v>
+        <v>0.1173024423291914</v>
       </c>
     </row>
     <row r="27">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04479861183336142</v>
+        <v>-0.04479861183336153</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611783258696416</v>
+        <v>0.1611783258696418</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7810550458340706</v>
+        <v>0.7810550458340705</v>
       </c>
     </row>
     <row r="28">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07528727625378238</v>
+        <v>-0.07528727625378254</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1614983128820298</v>
+        <v>0.16149831288203</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6410866959853159</v>
+        <v>0.6410866959853154</v>
       </c>
     </row>
     <row r="29">
@@ -2834,61 +2834,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09387617646092163</v>
+        <v>0.09387617646092151</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543340718197335</v>
+        <v>0.1543340718197336</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5430110331238927</v>
+        <v>0.5430110331238935</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002469929930368318</v>
+        <v>0.00631190808799797</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007130763690581516</v>
+        <v>0.006867343796543254</v>
       </c>
       <c r="D30" t="n">
-        <v>0.729059682342319</v>
+        <v>0.3580331856516396</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.004826402612991674</v>
+        <v>0.04715208655231704</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008314480096143233</v>
+        <v>0.04889616403699433</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5615898992578258</v>
+        <v>0.3348800057442116</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.003793322855986095</v>
+        <v>-0.002469929930368318</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02223202690000069</v>
+        <v>0.007130763690581495</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8645192309060578</v>
+        <v>0.7290596823423183</v>
       </c>
     </row>
     <row r="33">
@@ -2898,45 +2898,45 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2256479096144981</v>
+        <v>0.225647909614498</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1147189874002693</v>
+        <v>0.1147189874002692</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04918757099961338</v>
+        <v>0.04918757099961334</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.04715208655231709</v>
+        <v>-0.004826402612991652</v>
       </c>
       <c r="C34" t="n">
-        <v>0.04889616403699421</v>
+        <v>0.008314480096142945</v>
       </c>
       <c r="D34" t="n">
-        <v>0.33488000574421</v>
+        <v>0.5615898992578142</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.006311908087997961</v>
+        <v>-0.003793322855986125</v>
       </c>
       <c r="C35" t="n">
-        <v>0.006867343796543269</v>
+        <v>0.0222320269000006</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3580331856516412</v>
+        <v>0.8645192309060561</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.008</v>
+        <v>0.197</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001</v>
+        <v>0.064</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007</v>
+        <v>0.133</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.066</v>
+        <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.058</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008</v>
+        <v>0.044</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.054</v>
+        <v>-0.128</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.027</v>
+        <v>0.021</v>
       </c>
       <c r="E9" t="n">
-        <v>0.027</v>
+        <v>0.107</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.041</v>
+        <v>0.107</v>
       </c>
       <c r="D10" t="n">
-        <v>0.037</v>
+        <v>0.043</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004000000000000004</v>
+        <v>0.064</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.007</v>
+        <v>0.227</v>
       </c>
       <c r="D11" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.017</v>
+        <v>0.205</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.074</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>-0.003</v>
       </c>
       <c r="E12" t="n">
-        <v>0.034</v>
+        <v>-0.003</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.034</v>
+        <v>-0.066</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.008</v>
+        <v>-0.058</v>
       </c>
       <c r="E13" t="n">
-        <v>0.026</v>
+        <v>0.008</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.041</v>
+        <v>0.032</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.013</v>
+        <v>0.033</v>
       </c>
       <c r="E14" t="n">
-        <v>0.028</v>
+        <v>-0.001000000000000001</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.032</v>
+        <v>-0.054</v>
       </c>
       <c r="D15" t="n">
-        <v>0.033</v>
+        <v>-0.027</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.001000000000000001</v>
+        <v>0.027</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.023</v>
+        <v>0.041</v>
       </c>
       <c r="D16" t="n">
-        <v>0.006</v>
+        <v>0.037</v>
       </c>
       <c r="E16" t="n">
-        <v>0.017</v>
+        <v>0.004000000000000004</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.401</v>
+        <v>0.005</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.039</v>
+        <v>-0.013</v>
       </c>
       <c r="E17" t="n">
-        <v>0.362</v>
+        <v>-0.008</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.014</v>
+        <v>-0.008</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.143</v>
+        <v>0.022</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.044</v>
+        <v>0.015</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09899999999999999</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.019</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.022</v>
+        <v>-0</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.041</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>-0.013</v>
       </c>
       <c r="E21" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>-0.019</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.051</v>
+        <v>-0.022</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06200000000000001</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0</v>
+        <v>-0.113</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.003</v>
+        <v>-0.051</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.003</v>
+        <v>0.06200000000000001</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.022</v>
+        <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>0.015</v>
+        <v>-0.044</v>
       </c>
       <c r="E24" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.09899999999999999</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.024</v>
+        <v>-0.014</v>
       </c>
       <c r="D25" t="n">
-        <v>0.026</v>
+        <v>-0.002</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.001999999999999998</v>
+        <v>0.012</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.197</v>
+        <v>0.034</v>
       </c>
       <c r="D27" t="n">
-        <v>0.064</v>
+        <v>-0.008</v>
       </c>
       <c r="E27" t="n">
-        <v>0.133</v>
+        <v>0.026</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.046</v>
+        <v>-0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.002</v>
+        <v>0.026</v>
       </c>
       <c r="E28" t="n">
-        <v>0.044</v>
+        <v>-0.001999999999999998</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.227</v>
+        <v>0.023</v>
       </c>
       <c r="D29" t="n">
-        <v>0.022</v>
+        <v>0.006</v>
       </c>
       <c r="E29" t="n">
-        <v>0.205</v>
+        <v>0.017</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.005</v>
+        <v>-0.074</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.013</v>
+        <v>-0.04</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.008</v>
+        <v>0.034</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.107</v>
+        <v>0.392</v>
       </c>
       <c r="D31" t="n">
-        <v>0.043</v>
+        <v>0.029</v>
       </c>
       <c r="E31" t="n">
-        <v>0.064</v>
+        <v>0.363</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.128</v>
+        <v>0.007</v>
       </c>
       <c r="D32" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="E32" t="n">
-        <v>0.107</v>
+        <v>-0.017</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.392</v>
+        <v>-0.401</v>
       </c>
       <c r="D33" t="n">
-        <v>0.029</v>
+        <v>-0.039</v>
       </c>
       <c r="E33" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -1415,13 +1415,13 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7093.528441237814</v>
+        <v>7093.528441237813</v>
       </c>
       <c r="C2" t="n">
         <v>0.9958137312970582</v>
       </c>
       <c r="D2" t="n">
-        <v>0.13297606180212</v>
+        <v>0.1329760618021201</v>
       </c>
       <c r="E2" t="n">
         <v>1.68234909115562</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.588422507365228</v>
+        <v>1.588422507365227</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09950879751533108</v>
+        <v>0.09950879751533012</v>
       </c>
       <c r="D2" t="n">
-        <v>1.39338884809029</v>
+        <v>1.393388848090291</v>
       </c>
       <c r="E2" t="n">
-        <v>1.783456166640165</v>
+        <v>1.783456166640163</v>
       </c>
       <c r="F2" t="n">
-        <v>2.327001655354998e-57</v>
+        <v>2.327001655349488e-57</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002157202703634746</v>
+        <v>0.002157202703634755</v>
       </c>
       <c r="C3" t="n">
         <v>0.02004412832739044</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03712856691954959</v>
+        <v>-0.03712856691954958</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04144297232681908</v>
+        <v>0.04144297232681909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9142950096096353</v>
+        <v>0.9142950096096348</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.02806347567340356</v>
+        <v>-0.02806347567340357</v>
       </c>
       <c r="C4" t="n">
         <v>0.05180741466195352</v>
@@ -1550,10 +1550,10 @@
         <v>-0.1296041425429648</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07347719119615768</v>
+        <v>0.07347719119615767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5880331806434529</v>
+        <v>0.5880331806434527</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1566,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002136000897429317</v>
+        <v>0.002136000897429325</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0352189070159448</v>
+        <v>0.03521890701594482</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06689178842868751</v>
+        <v>-0.06689178842868755</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07116379022354616</v>
+        <v>0.0711637902235462</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9516385362649576</v>
+        <v>0.9516385362649575</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03303202308651724</v>
+        <v>0.03303202308651729</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03286800426819424</v>
+        <v>0.03286800426819425</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03138808152285224</v>
+        <v>-0.03138808152285221</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09745212769588671</v>
+        <v>0.09745212769588679</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3149015555617202</v>
+        <v>0.3149015555617194</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1616,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0152122870861078</v>
+        <v>-0.01521228708610778</v>
       </c>
       <c r="C7" t="n">
         <v>0.03536389523671277</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0845242481031124</v>
+        <v>-0.08452424810311238</v>
       </c>
       <c r="E7" t="n">
         <v>0.05409967393089682</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6670760911481436</v>
+        <v>0.6670760911481439</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1641,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01369113270818715</v>
+        <v>-0.01369113270818707</v>
       </c>
       <c r="C8" t="n">
         <v>0.03583749565076259</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08393133347979263</v>
+        <v>-0.08393133347979258</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05654906806341834</v>
+        <v>0.05654906806341843</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7024363340113144</v>
+        <v>0.7024363340113161</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1666,16 +1666,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02619917626172891</v>
+        <v>-0.02619917626172893</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03445373577537431</v>
+        <v>0.03445373577537433</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09372725751432176</v>
+        <v>-0.09372725751432182</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04132890499086394</v>
+        <v>0.04132890499086395</v>
       </c>
       <c r="F9" t="n">
         <v>0.4470058874486471</v>
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.124206443780099</v>
+        <v>-0.1242064437800987</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05548417525012692</v>
+        <v>0.0554841752501268</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2329534289822563</v>
+        <v>-0.2329534289822559</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01545945857794155</v>
+        <v>-0.01545945857794152</v>
       </c>
       <c r="F10" t="n">
         <v>0.02518246006139378</v>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07320420542333132</v>
+        <v>0.07320420542333141</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05628688228526354</v>
+        <v>0.05628688228526351</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03711605665783078</v>
+        <v>-0.03711605665783065</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1835244675044934</v>
+        <v>0.1835244675044935</v>
       </c>
       <c r="F11" t="n">
-        <v>0.193410701622554</v>
+        <v>0.1934107016225535</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1744,16 +1744,16 @@
         <v>-0.06076403853532326</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06002138315034827</v>
+        <v>0.06002138315034818</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1784037878122851</v>
+        <v>-0.1784037878122849</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05687571074163859</v>
+        <v>0.05687571074163843</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3113596568518616</v>
+        <v>0.3113596568518608</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.03935267962244716</v>
+        <v>-0.03935267962244713</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05702989918185167</v>
+        <v>0.0570298991818516</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1511292280608267</v>
+        <v>-0.1511292280608266</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07242386881593241</v>
+        <v>0.0724238688159323</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4901715914374866</v>
+        <v>0.4901715914374863</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.08994407386175092</v>
+        <v>-0.08994407386175075</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05595151464980275</v>
+        <v>0.05595151464980276</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1996070274558295</v>
+        <v>-0.1996070274558294</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01971887973232768</v>
+        <v>0.01971887973232787</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1079368395669098</v>
+        <v>0.1079368395669106</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.07972002010245767</v>
+        <v>-0.07972002010245759</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05482862722193887</v>
+        <v>0.05482862722193879</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1871821547792303</v>
+        <v>-0.18718215477923</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02774211457431491</v>
+        <v>0.02774211457431484</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1459503711242126</v>
+        <v>0.1459503711242125</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07580821482423769</v>
+        <v>-0.0758082148242375</v>
       </c>
       <c r="C16" t="n">
         <v>0.05391836373954741</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.181486265859081</v>
+        <v>-0.1814862658590808</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02986983621060563</v>
+        <v>0.02986983621060582</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1597296574439606</v>
+        <v>0.1597296574439617</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.007958708481944632</v>
+        <v>-0.007958708481944531</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05686585901762571</v>
+        <v>0.05686585901762579</v>
       </c>
       <c r="D17" t="n">
         <v>-0.1194137441064233</v>
       </c>
       <c r="E17" t="n">
-        <v>0.103496327142534</v>
+        <v>0.1034963271425343</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8886948895826451</v>
+        <v>0.8886948895826466</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02674600637292563</v>
+        <v>-0.02674600637292569</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05495082849883502</v>
+        <v>0.05495082849883496</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1344476511512795</v>
+        <v>-0.1344476511512794</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0809556384054282</v>
+        <v>0.08095563840542805</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6264523959201856</v>
+        <v>0.6264523959201845</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.08417048724369866</v>
+        <v>-0.08417048724369861</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05356575306273117</v>
+        <v>0.05356575306273116</v>
       </c>
       <c r="D19" t="n">
         <v>-0.1891574340514178</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02081645956402052</v>
+        <v>0.02081645956402056</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1161016281223215</v>
+        <v>0.1161016281223217</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1941,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1315545875635716</v>
+        <v>-0.1315545875635715</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05402663862558474</v>
+        <v>0.05402663862558477</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2374448534754783</v>
+        <v>-0.2374448534754782</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02566432165166498</v>
+        <v>-0.02566432165166481</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01489200108264303</v>
+        <v>0.01489200108264315</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1969,7 +1969,7 @@
         <v>-0.1243413906692296</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0561830384698433</v>
+        <v>0.05618303846984329</v>
       </c>
       <c r="D21" t="n">
         <v>-0.2344581226121508</v>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.07290986245855982</v>
+        <v>-0.07290986245855956</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05651076265826976</v>
+        <v>0.05651076265826971</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1836689220076595</v>
+        <v>-0.1836689220076592</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03784919709053987</v>
+        <v>0.03784919709054003</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1969832133925162</v>
+        <v>0.1969832133925173</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01550122276689241</v>
+        <v>-0.0155012227668923</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05392880208198828</v>
+        <v>0.0539288020819883</v>
       </c>
       <c r="D23" t="n">
         <v>-0.1211997325769781</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0901972870431933</v>
+        <v>0.09019728704319346</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7737764608404192</v>
+        <v>0.7737764608404208</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.01736702286559948</v>
+        <v>-0.01736702286559943</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04895754327588756</v>
+        <v>0.04895754327588754</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1133220444579002</v>
+        <v>-0.1133220444579001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07858799872670123</v>
+        <v>0.07858799872670125</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7227870755887478</v>
+        <v>0.7227870755887484</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01900414985650926</v>
+        <v>0.01900414985650929</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0256228364739088</v>
+        <v>0.02562283647390874</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03121568681411126</v>
+        <v>-0.03121568681411112</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06922398652712977</v>
+        <v>0.06922398652712969</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4582764034316501</v>
+        <v>0.4582764034316485</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.01136511239972224</v>
+        <v>-0.0113651123997223</v>
       </c>
       <c r="C26" t="n">
         <v>0.03076545132329945</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.07166428896150931</v>
+        <v>-0.07166428896150936</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04893406416206483</v>
+        <v>0.04893406416206476</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7118210062148216</v>
+        <v>0.71182100621482</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.008288872114817944</v>
+        <v>0.008288872114817953</v>
       </c>
       <c r="C27" t="n">
         <v>0.03118021288371118</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.05282322216754776</v>
+        <v>-0.05282322216754774</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06940096639718364</v>
+        <v>0.06940096639718366</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7903643050508879</v>
+        <v>0.7903643050508877</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.04441792109265476</v>
+        <v>0.04441792109265477</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0314722530820989</v>
+        <v>0.03147225308209887</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0172665614605888</v>
+        <v>-0.01726656146058872</v>
       </c>
       <c r="E28" t="n">
         <v>0.1061024036458983</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1581455893971989</v>
+        <v>0.1581455893971982</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.01111026890206916</v>
+        <v>-0.01111026890206912</v>
       </c>
       <c r="C29" t="n">
         <v>0.03230457849540543</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07442607928881094</v>
+        <v>-0.0744260792888109</v>
       </c>
       <c r="E29" t="n">
-        <v>0.05220554148467262</v>
+        <v>0.05220554148467266</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7309046284390834</v>
+        <v>0.7309046284390842</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2303472064753822</v>
+        <v>0.2303472064753823</v>
       </c>
       <c r="C30" t="n">
         <v>0.04274619914367982</v>
@@ -2203,7 +2203,7 @@
         <v>0.3141282172729716</v>
       </c>
       <c r="F30" t="n">
-        <v>7.096210791271882e-08</v>
+        <v>7.096210791271809e-08</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2216,19 +2216,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.001323773742398878</v>
+        <v>0.001323773742398876</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001449666664927174</v>
+        <v>0.001449666664927171</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.001517520710446678</v>
+        <v>-0.001517520710446673</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004165068195244434</v>
+        <v>0.004165068195244426</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3611598015227342</v>
+        <v>0.3611598015227337</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2237,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4907763416057432</v>
+        <v>0.009295972736054493</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01020349621388542</v>
+        <v>0.02351946149446091</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4707778565101369</v>
+        <v>-0.03680132472886548</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5107748267013494</v>
+        <v>0.05539327020097447</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.6926613581382872</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2262,23 +2262,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.001023762880892497</v>
+        <v>-0.0008847896531368747</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001412550988754018</v>
+        <v>0.001755881165775756</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003792311945176817</v>
+        <v>-0.004326253499189561</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001744786183391822</v>
+        <v>0.002556674192915811</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4685982250511579</v>
+        <v>0.6143311968318165</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2287,23 +2287,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.009295972736054522</v>
+        <v>0.4907763416057432</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02351946149446091</v>
+        <v>0.0102034962138854</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.03680132472886545</v>
+        <v>0.470777856510137</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0553932702009745</v>
+        <v>0.5107748267013494</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6926613581382863</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0008847896531368874</v>
+        <v>-0.001023762880892494</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001755881165775706</v>
+        <v>0.001412550988754021</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.004326253499189475</v>
+        <v>-0.003792311945176817</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0025566741929157</v>
+        <v>0.00174478618339183</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6143311968318013</v>
+        <v>0.4685982250511601</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2341,19 +2341,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.007684909964816873</v>
+        <v>-0.007684909964816872</v>
       </c>
       <c r="C36" t="n">
-        <v>0.004562970024586844</v>
+        <v>0.004562970024586898</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.01662816687554293</v>
+        <v>-0.01662816687554304</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001258346945909186</v>
+        <v>0.001258346945909293</v>
       </c>
       <c r="F36" t="n">
-        <v>0.09214489260396432</v>
+        <v>0.09214489260396824</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.820303044554362</v>
+        <v>-2.820303044554359</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5099234395092913</v>
+        <v>0.5099234395092808</v>
       </c>
       <c r="D2" t="n">
-        <v>3.18707735240834e-08</v>
+        <v>3.187077352406355e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02464939576457235</v>
+        <v>-0.02464939576457232</v>
       </c>
       <c r="C3" t="n">
         <v>0.1003099681595394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8058894933269581</v>
+        <v>0.8058894933269584</v>
       </c>
     </row>
     <row r="4">
@@ -2440,7 +2440,7 @@
         <v>0.2337176582603367</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3357703370011803</v>
+        <v>0.3357703370011802</v>
       </c>
     </row>
     <row r="5">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8191373674885463</v>
+        <v>0.8191373674885462</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734167828528219</v>
+        <v>0.1734167828528218</v>
       </c>
       <c r="D5" t="n">
-        <v>2.317989576597531e-06</v>
+        <v>2.317989576597514e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03652125765996336</v>
+        <v>0.0365212576599637</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1917132959179624</v>
+        <v>0.1917132959179623</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8489178549322636</v>
+        <v>0.8489178549322621</v>
       </c>
     </row>
     <row r="7">
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1068531552827689</v>
+        <v>0.1068531552827687</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1953287956048307</v>
+        <v>0.1953287956048305</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5843495250374455</v>
+        <v>0.5843495250374459</v>
       </c>
     </row>
     <row r="9">
@@ -2517,10 +2517,10 @@
         <v>0.8765772051307453</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1697332036095897</v>
+        <v>0.1697332036095895</v>
       </c>
       <c r="D9" t="n">
-        <v>2.411578475116438e-07</v>
+        <v>2.411578475116341e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04447986866030693</v>
+        <v>-0.04447986866030746</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604513322559264</v>
+        <v>0.2604513322559259</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8643967854929903</v>
+        <v>0.8643967854929884</v>
       </c>
     </row>
     <row r="11">
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2727472209256581</v>
+        <v>-0.2727472209256588</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2791278961561445</v>
+        <v>0.2791278961561441</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3284995130487427</v>
+        <v>0.3284995130487409</v>
       </c>
     </row>
     <row r="12">
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07889678868393106</v>
+        <v>0.07889678868393053</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596148796948633</v>
+        <v>0.259614879694863</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7612045862333778</v>
+        <v>0.7612045862333792</v>
       </c>
     </row>
     <row r="13">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04019393041481645</v>
+        <v>0.04019393041481586</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2574204041328311</v>
+        <v>0.2574204041328299</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8759217249006992</v>
+        <v>0.8759217249007004</v>
       </c>
     </row>
     <row r="14">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04910228165084252</v>
+        <v>-0.04910228165084306</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2612561015991035</v>
+        <v>0.2612561015991028</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8509182551619328</v>
+        <v>0.8509182551619308</v>
       </c>
     </row>
     <row r="15">
@@ -2610,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1160743543422993</v>
+        <v>0.1160743543422987</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2571236264961856</v>
+        <v>0.2571236264961847</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6516767631412993</v>
+        <v>0.6516767631412999</v>
       </c>
     </row>
     <row r="16">
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.002512421030225878</v>
+        <v>-0.002512421030226336</v>
       </c>
       <c r="C16" t="n">
-        <v>0.238607871750488</v>
+        <v>0.2386078717504878</v>
       </c>
       <c r="D16" t="n">
-        <v>0.991598831614466</v>
+        <v>0.9915988316144645</v>
       </c>
     </row>
     <row r="17">
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1088094847883377</v>
+        <v>0.1088094847883372</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2546184298925984</v>
+        <v>0.2546184298925981</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6691292855457321</v>
+        <v>0.6691292855457333</v>
       </c>
     </row>
     <row r="18">
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.137105462949366</v>
+        <v>-0.1371054629493665</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2637238215346601</v>
+        <v>0.2637238215346593</v>
       </c>
       <c r="D18" t="n">
-        <v>0.603145306032001</v>
+        <v>0.6031453060319985</v>
       </c>
     </row>
     <row r="19">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02469784288290738</v>
+        <v>-0.02469784288290792</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2529058254775164</v>
+        <v>0.2529058254775155</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9222052306173945</v>
+        <v>0.9222052306173925</v>
       </c>
     </row>
     <row r="20">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06845683158478712</v>
+        <v>-0.06845683158478774</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2673011584514008</v>
+        <v>0.2673011584514002</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7978707191500406</v>
+        <v>0.7978707191500383</v>
       </c>
     </row>
     <row r="21">
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2086621675742925</v>
+        <v>0.2086621675742919</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442815662419186</v>
+        <v>0.244281566241918</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3930013184626175</v>
+        <v>0.3930013184626177</v>
       </c>
     </row>
     <row r="22">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1754067081881009</v>
+        <v>-0.1754067081881016</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2700541998112392</v>
+        <v>0.2700541998112385</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5159996811704801</v>
+        <v>0.5159996811704775</v>
       </c>
     </row>
     <row r="23">
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.500438422493073</v>
+        <v>-0.5004384224930737</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870894861894652</v>
+        <v>0.2870894861894649</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08130839926920354</v>
+        <v>0.08130839926920294</v>
       </c>
     </row>
     <row r="24">
@@ -2773,10 +2773,10 @@
         <v>-0.5776000776467408</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143336799033598</v>
+        <v>0.1143336799033599</v>
       </c>
       <c r="D25" t="n">
-        <v>4.374815955439373e-07</v>
+        <v>4.374815955439421e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2357452695510327</v>
+        <v>0.2357452695510329</v>
       </c>
       <c r="C26" t="n">
         <v>0.1505208025229895</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1173024423291914</v>
+        <v>0.1173024423291908</v>
       </c>
     </row>
     <row r="27">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04479861183336153</v>
+        <v>-0.04479861183336157</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611783258696418</v>
+        <v>0.1611783258696417</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7810550458340705</v>
+        <v>0.7810550458340701</v>
       </c>
     </row>
     <row r="28">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07528727625378254</v>
+        <v>-0.07528727625378261</v>
       </c>
       <c r="C28" t="n">
-        <v>0.16149831288203</v>
+        <v>0.1614983128820299</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6410866959853154</v>
+        <v>0.6410866959853151</v>
       </c>
     </row>
     <row r="29">
@@ -2834,13 +2834,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09387617646092151</v>
+        <v>0.0938761764609214</v>
       </c>
       <c r="C29" t="n">
         <v>0.1543340718197336</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5430110331238935</v>
+        <v>0.543011033123894</v>
       </c>
     </row>
     <row r="30">
@@ -2850,77 +2850,77 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.00631190808799797</v>
+        <v>0.006311908087997971</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006867343796543254</v>
+        <v>0.006867343796543258</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3580331856516396</v>
+        <v>0.3580331856516399</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.04715208655231704</v>
+        <v>0.2256479096144979</v>
       </c>
       <c r="C31" t="n">
-        <v>0.04889616403699433</v>
+        <v>0.1147189874002692</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3348800057442116</v>
+        <v>0.04918757099961338</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002469929930368318</v>
+        <v>-0.004826402612991677</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007130763690581495</v>
+        <v>0.008314480096142876</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7290596823423183</v>
+        <v>0.5615898992578088</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.225647909614498</v>
+        <v>0.04715208655231691</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1147189874002692</v>
+        <v>0.04889616403699417</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04918757099961334</v>
+        <v>0.3348800057442113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.004826402612991652</v>
+        <v>-0.002469929930368334</v>
       </c>
       <c r="C34" t="n">
-        <v>0.008314480096142945</v>
+        <v>0.007130763690581494</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5615898992578142</v>
+        <v>0.7290596823423166</v>
       </c>
     </row>
     <row r="35">
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.003793322855986125</v>
+        <v>-0.003793322855986162</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0222320269000006</v>
+        <v>0.02223202690000054</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8645192309060561</v>
+        <v>0.8645192309060545</v>
       </c>
     </row>
   </sheetData>
